--- a/archivos/formularios/formulario6.xlsx
+++ b/archivos/formularios/formulario6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\fmt\archivos\formularios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.mora\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB6E5762-F51C-4E1E-AB7D-661ADE7DB42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D504F5DA-8366-4860-B70E-25740097C4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{84B57277-5B34-44BE-8D0D-3FBDEC85E1AD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{84B57277-5B34-44BE-8D0D-3FBDEC85E1AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -151,7 +151,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -175,21 +175,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -207,7 +196,7 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -225,7 +214,52 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -234,21 +268,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -256,36 +275,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -297,159 +286,10 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -458,113 +298,74 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -963,464 +764,609 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16E93D07-64CA-4377-8F70-C0039D344657}">
-  <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="15.90625" customWidth="1"/>
-    <col min="7" max="7" width="16.6328125" customWidth="1"/>
-    <col min="8" max="8" width="20.08984375" customWidth="1"/>
-    <col min="9" max="9" width="16.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.7265625" customWidth="1"/>
-    <col min="12" max="12" width="13.7265625" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="20.109375" customWidth="1"/>
+    <col min="9" max="9" width="16.5546875" customWidth="1"/>
+    <col min="10" max="10" width="13.77734375" customWidth="1"/>
+    <col min="12" max="12" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="3" t="s">
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="11"/>
-      <c r="L1" s="4"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="21"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="2" t="s">
+      <c r="K1" s="13"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="20"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="11">
         <v>2</v>
       </c>
-      <c r="K2" s="9"/>
-      <c r="L2" s="5"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="21"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="2" t="s">
+      <c r="K2" s="11"/>
+      <c r="L2" s="12"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="20"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="9">
         <v>44644</v>
       </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="6"/>
-    </row>
-    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="26"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="31" t="s">
+      <c r="K3" s="9"/>
+      <c r="L3" s="10"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="20"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="32"/>
-      <c r="L4" s="27"/>
-    </row>
-    <row r="5" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="33" t="s">
+      <c r="K4" s="11"/>
+      <c r="L4" s="12"/>
+    </row>
+    <row r="5" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="35"/>
-    </row>
-    <row r="6" spans="1:12" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="33" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="26"/>
+    </row>
+    <row r="6" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="33" t="s">
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="35"/>
-    </row>
-    <row r="7" spans="1:12" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="39" t="s">
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="26"/>
+    </row>
+    <row r="7" spans="1:12" ht="41.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="41" t="s">
+      <c r="C7" s="23"/>
+      <c r="D7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="41" t="s">
+      <c r="G7" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="41" t="s">
+      <c r="I7" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="41" t="s">
+      <c r="J7" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="41" t="s">
+      <c r="K7" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="42" t="s">
+      <c r="L7" s="28" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="36"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="43"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" s="7"/>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="7"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="17"/>
+      <c r="F9" s="5"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="17"/>
+      <c r="H9" s="5"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
-      <c r="L9" s="44"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" s="7"/>
+      <c r="L9" s="7"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="17"/>
+      <c r="F10" s="5"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="17"/>
+      <c r="H10" s="5"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
-      <c r="L10" s="44"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="7"/>
+      <c r="L10" s="7"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-      <c r="F11" s="17"/>
+      <c r="F11" s="5"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="17"/>
+      <c r="H11" s="5"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="L11" s="44"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="7"/>
+      <c r="L11" s="7"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="17"/>
+      <c r="F12" s="5"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="17"/>
+      <c r="H12" s="5"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="44"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="7"/>
+      <c r="L12" s="7"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="17"/>
+      <c r="F13" s="5"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="17"/>
+      <c r="H13" s="5"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="44"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" s="7"/>
+      <c r="L13" s="7"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="17"/>
+      <c r="F14" s="5"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="17"/>
+      <c r="H14" s="5"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="44"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="7"/>
+      <c r="L14" s="7"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="17"/>
+      <c r="F15" s="5"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="17"/>
+      <c r="H15" s="5"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="44"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" s="7"/>
+      <c r="L15" s="7"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="17"/>
+      <c r="F16" s="5"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="17"/>
+      <c r="H16" s="5"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="44"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17" s="7"/>
+      <c r="L16" s="7"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="17"/>
+      <c r="F17" s="5"/>
       <c r="G17" s="1"/>
-      <c r="H17" s="17"/>
+      <c r="H17" s="5"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-      <c r="L17" s="44"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18" s="7"/>
+      <c r="L17" s="7"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="17"/>
+      <c r="F18" s="5"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="17"/>
+      <c r="H18" s="5"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="44"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19" s="7"/>
+      <c r="L18" s="7"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="17"/>
+      <c r="F19" s="5"/>
       <c r="G19" s="1"/>
-      <c r="H19" s="17"/>
+      <c r="H19" s="5"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="44"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20" s="7"/>
+      <c r="L19" s="7"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="17"/>
+      <c r="F20" s="5"/>
       <c r="G20" s="1"/>
-      <c r="H20" s="17"/>
+      <c r="H20" s="5"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="44"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21" s="7"/>
+      <c r="L20" s="7"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
-      <c r="F21" s="17"/>
+      <c r="F21" s="5"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="17"/>
+      <c r="H21" s="5"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="44"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22" s="7"/>
+      <c r="L21" s="7"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="17"/>
+      <c r="F22" s="5"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="17"/>
+      <c r="H22" s="5"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="44"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23" s="7"/>
+      <c r="L22" s="7"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="17"/>
+      <c r="F23" s="5"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="17"/>
+      <c r="H23" s="5"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="44"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24" s="7"/>
+      <c r="L23" s="7"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="17"/>
+      <c r="F24" s="5"/>
       <c r="G24" s="1"/>
-      <c r="H24" s="17"/>
+      <c r="H24" s="5"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="44"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25" s="7"/>
+      <c r="L24" s="7"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="17"/>
+      <c r="F25" s="5"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="17"/>
+      <c r="H25" s="5"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="44"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26" s="7"/>
+      <c r="L25" s="7"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="17"/>
+      <c r="F26" s="5"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="17"/>
+      <c r="H26" s="5"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-      <c r="L26" s="44"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27" s="7"/>
+      <c r="L26" s="7"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="17"/>
+      <c r="F27" s="5"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="17"/>
+      <c r="H27" s="5"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-      <c r="L27" s="44"/>
-    </row>
-    <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="8"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="45"/>
+      <c r="L27" s="7"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="7"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="7"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="7"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="7"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="7"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="2"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="7"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="7"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="2"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="7"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="7"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="2"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="7"/>
+    </row>
+    <row r="38" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="3"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="B24:C24"/>
+  <mergeCells count="41">
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
@@ -1437,6 +1383,11 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B7:C7"/>
